--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0002T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.483110741815489</v>
+        <v>0.728505495545017</v>
       </c>
       <c r="D2" t="n">
-        <v>5.872536539058084</v>
+        <v>0.9542871875969386</v>
       </c>
       <c r="E2" t="n">
-        <v>23.08582231716485</v>
+        <v>3.751446126539289</v>
       </c>
       <c r="F2" t="n">
-        <v>22.42834553697843</v>
+        <v>3.644606149758995</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.0007116551977</v>
+        <v>8.612615643969626</v>
       </c>
       <c r="D3" t="n">
-        <v>52.55435527765255</v>
+        <v>8.54008273261854</v>
       </c>
       <c r="E3" t="n">
-        <v>23.08582231716485</v>
+        <v>3.751446126539289</v>
       </c>
       <c r="F3" t="n">
-        <v>22.42834553697843</v>
+        <v>3.644606149758995</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.19292876066525</v>
+        <v>7.181350923608104</v>
       </c>
       <c r="D4" t="n">
-        <v>43.74655195062167</v>
+        <v>7.108814691976022</v>
       </c>
       <c r="E4" t="n">
-        <v>23.08582231716485</v>
+        <v>3.751446126539289</v>
       </c>
       <c r="F4" t="n">
-        <v>22.42834553697843</v>
+        <v>3.644606149758995</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.04326545333431</v>
+        <v>9.269530636166825</v>
       </c>
       <c r="D5" t="n">
-        <v>56.61002664954851</v>
+        <v>9.199129330551633</v>
       </c>
       <c r="E5" t="n">
-        <v>23.08582231716485</v>
+        <v>3.751446126539289</v>
       </c>
       <c r="F5" t="n">
-        <v>22.42834553697843</v>
+        <v>3.644606149758995</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>73.71425298101049</v>
+        <v>11.9785661094142</v>
       </c>
       <c r="D6" t="n">
-        <v>73.29828879961707</v>
+        <v>11.91097192993777</v>
       </c>
       <c r="E6" t="n">
-        <v>23.08582231716485</v>
+        <v>3.751446126539289</v>
       </c>
       <c r="F6" t="n">
-        <v>22.42834553697843</v>
+        <v>3.644606149758995</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
